--- a/individual_Tests/write/write_test_results.xlsx
+++ b/individual_Tests/write/write_test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge\Desktop\Masters\Tests\initial_tests\individual_Tests\write\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F2EDB5-76A4-477A-B731-BE652CE5F918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E140771-4F55-4BC5-B2D5-F9FDC8CFE62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="80">
   <si>
     <t>Test ID</t>
   </si>
@@ -259,13 +259,11 @@
     <t>Patched?</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Kinda, needs overhaul</t>
+    <t xml:space="preserve">Yes, 
+b4031ba </t>
   </si>
 </sst>
 </file>
@@ -824,7 +822,7 @@
         <v>75</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1045,7 +1043,7 @@
         <v>73</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
@@ -1074,7 +1072,7 @@
         <v>76</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
